--- a/PYPL_Model.xlsx
+++ b/PYPL_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Financials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F40303-5849-45C8-B505-C8B19542B5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5724463-0EBA-4828-9027-BF5EB9B02C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="2107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="2106">
   <si>
     <t>Master</t>
   </si>
@@ -7505,9 +7505,6 @@
     <t>Projected ROIC:</t>
   </si>
   <si>
-    <t>8/2/2025</t>
-  </si>
-  <si>
     <t>Change Δ</t>
   </si>
   <si>
@@ -7610,13 +7607,13 @@
     <t>Q4 2027</t>
   </si>
   <si>
-    <t>10/31/25</t>
-  </si>
-  <si>
     <t>Founder(s): Peter Thiel, Max Levchin, Luke Nosek, Ken Howery, Yu Pan, Elon Musk</t>
   </si>
   <si>
     <t>(408) 967 - 7000</t>
+  </si>
+  <si>
+    <t>1/10/2025</t>
   </si>
 </sst>
 </file>
@@ -14878,10 +14875,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="80">
-        <v>69.27</v>
+        <v>57.8</v>
       </c>
       <c r="D5" s="82" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -14892,7 +14889,7 @@
         <v>935.65</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -14901,7 +14898,7 @@
       </c>
       <c r="C7" s="81">
         <f>C5*C6</f>
-        <v>64812.475499999993</v>
+        <v>54080.569999999992</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -14913,7 +14910,7 @@
         <v>10755</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -14924,7 +14921,7 @@
         <v>11276</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -14933,7 +14930,7 @@
       </c>
       <c r="C10" s="81">
         <f>C7-C8+C9</f>
-        <v>65333.475499999993</v>
+        <v>54601.569999999992</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="15">
@@ -14943,7 +14940,7 @@
     </row>
     <row r="14" spans="1:21" ht="15">
       <c r="B14" s="1" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>7</v>
@@ -14961,7 +14958,7 @@
         <v>134</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>9</v>
@@ -15009,7 +15006,7 @@
         <v>128</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>129</v>
@@ -15053,7 +15050,7 @@
     </row>
     <row r="22" spans="1:21" ht="15">
       <c r="B22" s="2" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="15">
@@ -15066,17 +15063,17 @@
     </row>
     <row r="25" spans="1:21" ht="15">
       <c r="B25" s="1" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="C26" s="1" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15">
       <c r="B27" s="1" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15">
@@ -15413,9 +15410,6 @@
     <hyperlink ref="T16" r:id="rId6" xr:uid="{DD4F737D-F0DE-4E57-9A8C-74C21CB7FABF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D5" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId7"/>
 </worksheet>
 </file>
@@ -15620,13 +15614,13 @@
         <v>277</v>
       </c>
       <c r="AZ3" s="33" t="s">
+        <v>2100</v>
+      </c>
+      <c r="BA3" s="33" t="s">
         <v>2101</v>
       </c>
-      <c r="BA3" s="33" t="s">
+      <c r="BB3" s="33" t="s">
         <v>2102</v>
-      </c>
-      <c r="BB3" s="33" t="s">
-        <v>2103</v>
       </c>
       <c r="BG3" s="2">
         <v>2015</v>
@@ -24638,11 +24632,9 @@
       </c>
       <c r="BZ66" s="70">
         <f>Main!C5</f>
-        <v>69.27</v>
-      </c>
-      <c r="CA66" s="75" t="s">
-        <v>2093</v>
-      </c>
+        <v>57.8</v>
+      </c>
+      <c r="CA66" s="75"/>
       <c r="CB66" s="56"/>
       <c r="CC66" s="56"/>
       <c r="CD66" s="56"/>
@@ -24714,11 +24706,11 @@
       <c r="BW67" s="63"/>
       <c r="BX67" s="63"/>
       <c r="BY67" s="60" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="BZ67" s="65">
         <f>BZ65/BZ66-1</f>
-        <v>0.26014010573355595</v>
+        <v>0.5102059710062874</v>
       </c>
       <c r="CA67" s="74" t="str">
         <f>IF(BZ67&gt;0,"Upside","Downside")</f>
